--- a/erp-server/erp-server-oms/src/main/resources/excel/exhibitionOrderTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/exhibitionOrderTemplate.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <r>
       <rPr>
@@ -114,6 +114,20 @@
         <scheme val="minor"/>
       </rPr>
       <t>领用人</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>销售部门</t>
     </r>
   </si>
   <si>
@@ -1755,28 +1769,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.6333333333333" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.0916666666667" style="1" customWidth="1"/>
     <col min="3" max="3" width="17.8166666666667" style="1" customWidth="1"/>
     <col min="4" max="4" width="20.0916666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.8166666666667" style="1" customWidth="1"/>
-    <col min="8" max="24" width="20.9083333333333" style="1" customWidth="1"/>
-    <col min="25" max="25" width="17.725" style="1" customWidth="1"/>
-    <col min="26" max="27" width="15.5416666666667" style="1" customWidth="1"/>
-    <col min="28" max="28" width="19.725" style="1" customWidth="1"/>
-    <col min="29" max="29" width="14.1833333333333" style="1" customWidth="1"/>
-    <col min="30" max="30" width="14.275" style="1" customWidth="1"/>
-    <col min="31" max="31" width="14" style="1" customWidth="1"/>
-    <col min="32" max="32" width="12.9083333333333" style="1" customWidth="1"/>
-    <col min="33" max="33" width="19.8166666666667" style="1" customWidth="1"/>
+    <col min="5" max="6" width="17" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.8166666666667" style="1" customWidth="1"/>
+    <col min="9" max="25" width="20.9083333333333" style="1" customWidth="1"/>
+    <col min="26" max="26" width="17.725" style="1" customWidth="1"/>
+    <col min="27" max="28" width="15.5416666666667" style="1" customWidth="1"/>
+    <col min="29" max="29" width="19.725" style="1" customWidth="1"/>
+    <col min="30" max="30" width="14.1833333333333" style="1" customWidth="1"/>
+    <col min="31" max="31" width="14.275" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14" style="1" customWidth="1"/>
+    <col min="33" max="33" width="12.9083333333333" style="1" customWidth="1"/>
+    <col min="34" max="34" width="19.8166666666667" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:34">
+    <row r="1" ht="14.25" spans="1:35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1807,7 +1821,7 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="3" t="s">
@@ -1822,16 +1836,16 @@
       <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="S1" s="5" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="6" t="s">
@@ -1840,19 +1854,19 @@
       <c r="U1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="W1" s="5" t="s">
         <v>22</v>
       </c>
       <c r="X1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="AA1" s="4" t="s">
@@ -1861,42 +1875,45 @@
       <c r="AB1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AC1" s="4" t="s">
         <v>28</v>
       </c>
       <c r="AD1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="7" t="s">
+      <c r="AE1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="4" t="s">
+      <c r="AF1" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="5" t="s">
+      <c r="AG1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="8"/>
+      <c r="AH1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y1">
       <formula1>"网店销售收款,预收100%,货到收款,多到期日(按金额),月结30天,分期付款,30天后收款"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE1:AF1 C2:C1048576 U2:U1048576 L2:M1048576 H2:J1048576 O2:S1048576"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K1048576 V$1:V$1048576 AF2:AF1048576">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF1:AG1 C2:C1048576 V2:V1048576 M2:N1048576 I2:K1048576 P2:T1048576"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L1048576 W$1:W$1048576 AG2:AG1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576">
       <formula1>"EXW,FOB,FCA,DAP,DDU,DDP"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T$1:T$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U$1:U$1048576">
       <formula1>"自提,发货"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W$1:W$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X$1:X$1048576">
       <formula1>"货代地址,收货地址,公司地址"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y1048576">
       <formula1>"网店销售收款,预收100%,货到收款,多到期日（按金额）,月结30天,分期付款,30天收收款"</formula1>
     </dataValidation>
   </dataValidations>
